--- a/Power BI_vendas por mes.xlsx
+++ b/Power BI_vendas por mes.xlsx
@@ -405,7 +405,7 @@
         <v>2015</v>
       </c>
       <c r="D2">
-        <v>28828.254</v>
+        <v>14205.707</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -419,7 +419,7 @@
         <v>2016</v>
       </c>
       <c r="D3">
-        <v>29347.3864</v>
+        <v>18066.9576</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -433,7 +433,7 @@
         <v>2017</v>
       </c>
       <c r="D4">
-        <v>38048.184</v>
+        <v>18542.491</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -447,7 +447,7 @@
         <v>2018</v>
       </c>
       <c r="D5">
-        <v>59767.091</v>
+        <v>43476.474</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -461,7 +461,7 @@
         <v>2015</v>
       </c>
       <c r="D6">
-        <v>12588.484</v>
+        <v>4519.892</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -475,7 +475,7 @@
         <v>2016</v>
       </c>
       <c r="D7">
-        <v>20728.352</v>
+        <v>11951.411</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -489,7 +489,7 @@
         <v>2017</v>
       </c>
       <c r="D8">
-        <v>48907.59</v>
+        <v>22978.815</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -503,7 +503,7 @@
         <v>2018</v>
       </c>
       <c r="D9">
-        <v>48928.8334</v>
+        <v>19920.9974</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -517,7 +517,7 @@
         <v>2015</v>
       </c>
       <c r="D10">
-        <v>54027.692</v>
+        <v>55205.797</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -531,7 +531,7 @@
         <v>2016</v>
       </c>
       <c r="D11">
-        <v>34489.6776</v>
+        <v>32339.3184</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -545,7 +545,7 @@
         <v>2017</v>
       </c>
       <c r="D12">
-        <v>48990.141</v>
+        <v>51165.059</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -559,7 +559,7 @@
         <v>2018</v>
       </c>
       <c r="D13">
-        <v>74748.6238</v>
+        <v>58863.4128</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -573,7 +573,7 @@
         <v>2015</v>
       </c>
       <c r="D14">
-        <v>24710.016</v>
+        <v>27906.855</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -587,7 +587,7 @@
         <v>2016</v>
       </c>
       <c r="D15">
-        <v>38056.9685</v>
+        <v>34154.4685</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -601,7 +601,7 @@
         <v>2017</v>
       </c>
       <c r="D16">
-        <v>42368.048</v>
+        <v>38679.767</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -615,7 +615,7 @@
         <v>2018</v>
       </c>
       <c r="D17">
-        <v>37849.2156</v>
+        <v>35541.9101</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -629,7 +629,7 @@
         <v>2015</v>
       </c>
       <c r="D18">
-        <v>29520.49</v>
+        <v>23644.303</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -643,7 +643,7 @@
         <v>2016</v>
       </c>
       <c r="D19">
-        <v>30761.5585</v>
+        <v>29959.5305</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -657,7 +657,7 @@
         <v>2017</v>
       </c>
       <c r="D20">
-        <v>64836.2518</v>
+        <v>56656.908</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -671,7 +671,7 @@
         <v>2018</v>
       </c>
       <c r="D21">
-        <v>40882.4464</v>
+        <v>43825.9822</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -685,7 +685,7 @@
         <v>2015</v>
       </c>
       <c r="D22">
-        <v>29181.3346</v>
+        <v>34322.9356</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -699,7 +699,7 @@
         <v>2016</v>
       </c>
       <c r="D23">
-        <v>28515.9082</v>
+        <v>23599.374</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -713,7 +713,7 @@
         <v>2017</v>
       </c>
       <c r="D24">
-        <v>37424.681</v>
+        <v>39724.486</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -727,7 +727,7 @@
         <v>2018</v>
       </c>
       <c r="D25">
-        <v>46912.8475</v>
+        <v>48190.7277</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -741,7 +741,7 @@
         <v>2015</v>
       </c>
       <c r="D26">
-        <v>35194.558</v>
+        <v>33781.543</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -755,7 +755,7 @@
         <v>2016</v>
       </c>
       <c r="D27">
-        <v>28573.31</v>
+        <v>28608.259</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -769,7 +769,7 @@
         <v>2017</v>
       </c>
       <c r="D28">
-        <v>41761.943</v>
+        <v>38320.783</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -783,7 +783,7 @@
         <v>2018</v>
       </c>
       <c r="D29">
-        <v>53942.7755</v>
+        <v>44825.104</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -797,7 +797,7 @@
         <v>2015</v>
       </c>
       <c r="D30">
-        <v>37349.2655</v>
+        <v>27117.5365</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -811,7 +811,7 @@
         <v>2016</v>
       </c>
       <c r="D31">
-        <v>49076.93</v>
+        <v>36818.3422</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -825,7 +825,7 @@
         <v>2017</v>
       </c>
       <c r="D32">
-        <v>45766.8144</v>
+        <v>30542.2003</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -839,7 +839,7 @@
         <v>2018</v>
       </c>
       <c r="D33">
-        <v>75408.784</v>
+        <v>62837.848</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -853,7 +853,7 @@
         <v>2015</v>
       </c>
       <c r="D34">
-        <v>65956.3998</v>
+        <v>81623.52680000001</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -867,7 +867,7 @@
         <v>2016</v>
       </c>
       <c r="D35">
-        <v>65352.997</v>
+        <v>63133.606</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -881,7 +881,7 @@
         <v>2017</v>
       </c>
       <c r="D36">
-        <v>40692.3063</v>
+        <v>69193.3909</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -895,7 +895,7 @@
         <v>2018</v>
       </c>
       <c r="D37">
-        <v>73153.364</v>
+        <v>86152.88800000001</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -909,7 +909,7 @@
         <v>2015</v>
       </c>
       <c r="D38">
-        <v>34561.947</v>
+        <v>31453.393</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -923,7 +923,7 @@
         <v>2016</v>
       </c>
       <c r="D39">
-        <v>31631.889</v>
+        <v>31011.7375</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -937,7 +937,7 @@
         <v>2017</v>
       </c>
       <c r="D40">
-        <v>52156.958</v>
+        <v>59583.033</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -951,7 +951,7 @@
         <v>2018</v>
       </c>
       <c r="D41">
-        <v>65501.1622</v>
+        <v>77448.1312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -965,7 +965,7 @@
         <v>2015</v>
       </c>
       <c r="D42">
-        <v>64369.4565</v>
+        <v>77907.66070000001</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -979,7 +979,7 @@
         <v>2016</v>
       </c>
       <c r="D43">
-        <v>50009.145</v>
+        <v>75249.3995</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -993,7 +993,7 @@
         <v>2017</v>
       </c>
       <c r="D44">
-        <v>66392.54700000001</v>
+        <v>79066.4958</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1007,7 +1007,7 @@
         <v>2018</v>
       </c>
       <c r="D45">
-        <v>87997.64</v>
+        <v>117938.155</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1021,7 +1021,7 @@
         <v>2015</v>
       </c>
       <c r="D46">
-        <v>63568.3107</v>
+        <v>68167.0585</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1035,7 +1035,7 @@
         <v>2016</v>
       </c>
       <c r="D47">
-        <v>52891.8832</v>
+        <v>74543.6012</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1049,7 +1049,7 @@
         <v>2017</v>
       </c>
       <c r="D48">
-        <v>72847.0855</v>
+        <v>95739.121</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1063,7 +1063,7 @@
         <v>2018</v>
       </c>
       <c r="D49">
-        <v>56959.2358</v>
+        <v>83030.3888</v>
       </c>
     </row>
   </sheetData>
